--- a/refs/heads/main/StructureDefinition-CertDIVOC.xlsx
+++ b/refs/heads/main/StructureDefinition-CertDIVOC.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T21:40:28+00:00</t>
+    <t>2023-12-14T13:07:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-CertDIVOC.xlsx
+++ b/refs/heads/main/StructureDefinition-CertDIVOC.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-14T13:07:01+00:00</t>
+    <t>2023-12-14T13:50:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-CertDIVOC.xlsx
+++ b/refs/heads/main/StructureDefinition-CertDIVOC.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-14T13:50:56+00:00</t>
+    <t>2023-12-15T03:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-CertDIVOC.xlsx
+++ b/refs/heads/main/StructureDefinition-CertDIVOC.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T03:05:37+00:00</t>
+    <t>2024-01-19T16:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-CertDIVOC.xlsx
+++ b/refs/heads/main/StructureDefinition-CertDIVOC.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2970" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2879" uniqueCount="284">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T16:18:21+00:00</t>
+    <t>2024-04-24T00:11:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -223,9 +223,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>CertDIVOC.credentialSubject.extension</t>
   </si>
   <si>
@@ -286,9 +283,6 @@
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>CertDIVOC.credentialSubject.type</t>
   </si>
   <si>
@@ -605,9 +599,6 @@
     <t>Address.use</t>
   </si>
   <si>
-    <t>unique(./use)</t>
-  </si>
-  <si>
     <t>CertDIVOC.evidence.facility.address.type</t>
   </si>
   <si>
@@ -653,9 +644,6 @@
     <t>Address.text</t>
   </si>
   <si>
-    <t>./formatted</t>
-  </si>
-  <si>
     <t>CertDIVOC.evidence.facility.address.line</t>
   </si>
   <si>
@@ -669,9 +657,6 @@
   </si>
   <si>
     <t>Address.line</t>
-  </si>
-  <si>
-    <t>AD.part[parttype = AL]</t>
   </si>
   <si>
     <t>CertDIVOC.evidence.facility.address.city</t>
@@ -687,9 +672,6 @@
     <t>Address.city</t>
   </si>
   <si>
-    <t>AD.part[parttype = CTY]</t>
-  </si>
-  <si>
     <t>CertDIVOC.evidence.facility.address.district</t>
   </si>
   <si>
@@ -706,9 +688,6 @@
     <t>Address.district</t>
   </si>
   <si>
-    <t>AD.part[parttype = CNT | CPA]</t>
-  </si>
-  <si>
     <t>CertDIVOC.evidence.facility.address.state</t>
   </si>
   <si>
@@ -722,9 +701,6 @@
     <t>Address.state</t>
   </si>
   <si>
-    <t>AD.part[parttype = STA]</t>
-  </si>
-  <si>
     <t>CertDIVOC.evidence.facility.address.postalCode</t>
   </si>
   <si>
@@ -738,9 +714,6 @@
     <t>Address.postalCode</t>
   </si>
   <si>
-    <t>AD.part[parttype = ZIP]</t>
-  </si>
-  <si>
     <t>CertDIVOC.evidence.facility.address.country</t>
   </si>
   <si>
@@ -754,9 +727,6 @@
   </si>
   <si>
     <t>Address.country</t>
-  </si>
-  <si>
-    <t>AD.part[parttype = CNT]</t>
   </si>
   <si>
     <t>CertDIVOC.evidence.facility.address.period</t>
@@ -782,9 +752,6 @@
   </si>
   <si>
     <t>Address.period</t>
-  </si>
-  <si>
-    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
   </si>
   <si>
     <t>CertDIVOC.evidence.facility.address.streetAddress</t>
@@ -1227,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK91"/>
+  <dimension ref="A1:AJ91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.51953125" customWidth="true" bestFit="true"/>
@@ -1264,7 +1231,6 @@
     <col min="3" max="3" hidden="true" width="8.0" customWidth="false"/>
     <col min="17" max="17" width="20.703125" customWidth="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="30.98828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1366,9 +1332,6 @@
       <c r="AJ1" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="AK1" t="s" s="2">
-        <v>36</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
@@ -1469,9 +1432,6 @@
       <c r="AJ2" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="AK2" t="s" s="2">
-        <v>36</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -1572,9 +1532,6 @@
       <c r="AJ3" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="AK3" t="s" s="2">
-        <v>36</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -1675,9 +1632,6 @@
       <c r="AJ4" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="AK4" t="s" s="2">
-        <v>36</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -1778,9 +1732,6 @@
       <c r="AJ5" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="AK5" t="s" s="2">
-        <v>36</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -1881,9 +1832,6 @@
       <c r="AJ6" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="AK6" t="s" s="2">
-        <v>36</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -1984,9 +1932,6 @@
       <c r="AJ7" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="AK7" t="s" s="2">
-        <v>36</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -2087,20 +2032,17 @@
       <c r="AJ8" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="AK8" t="s" s="2">
-        <v>66</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2119,16 +2061,16 @@
         <v>36</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>69</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>71</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>72</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2166,19 +2108,19 @@
         <v>36</v>
       </c>
       <c r="AB9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC9" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="AC9" t="s" s="2">
+      <c r="AD9" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE9" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="AD9" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AE9" t="s" s="2">
+      <c r="AF9" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>37</v>
@@ -2190,22 +2132,19 @@
         <v>36</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK9" t="s" s="2">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2218,25 +2157,25 @@
         <v>36</v>
       </c>
       <c r="I10" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K10" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="J10" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K10" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>36</v>
@@ -2285,7 +2224,7 @@
         <v>36</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>37</v>
@@ -2297,18 +2236,15 @@
         <v>36</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK10" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2334,10 +2270,10 @@
         <v>43</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2388,7 +2324,7 @@
         <v>36</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>42</v>
@@ -2402,16 +2338,13 @@
       <c r="AJ11" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="AK11" t="s" s="2">
-        <v>36</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2437,10 +2370,10 @@
         <v>43</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2491,7 +2424,7 @@
         <v>36</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>37</v>
@@ -2503,18 +2436,15 @@
         <v>36</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK12" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2540,10 +2470,10 @@
         <v>43</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2594,7 +2524,7 @@
         <v>36</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>37</v>
@@ -2606,18 +2536,15 @@
         <v>36</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK13" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2643,10 +2570,10 @@
         <v>43</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2697,7 +2624,7 @@
         <v>36</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>37</v>
@@ -2709,18 +2636,15 @@
         <v>36</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK14" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2746,10 +2670,10 @@
         <v>43</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2800,7 +2724,7 @@
         <v>36</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>37</v>
@@ -2812,18 +2736,15 @@
         <v>36</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK15" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2849,10 +2770,10 @@
         <v>43</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2903,7 +2824,7 @@
         <v>36</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>37</v>
@@ -2915,18 +2836,15 @@
         <v>36</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK16" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2952,10 +2870,10 @@
         <v>43</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3006,7 +2924,7 @@
         <v>36</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>37</v>
@@ -3018,18 +2936,15 @@
         <v>36</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK17" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3052,13 +2967,13 @@
         <v>36</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3109,7 +3024,7 @@
         <v>36</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>37</v>
@@ -3121,18 +3036,15 @@
         <v>36</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK18" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3158,10 +3070,10 @@
         <v>43</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3212,7 +3124,7 @@
         <v>36</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>37</v>
@@ -3224,18 +3136,15 @@
         <v>36</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK19" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3261,10 +3170,10 @@
         <v>59</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3315,7 +3224,7 @@
         <v>36</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>37</v>
@@ -3329,16 +3238,13 @@
       <c r="AJ20" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="AK20" t="s" s="2">
-        <v>36</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3364,10 +3270,10 @@
         <v>43</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3432,20 +3338,17 @@
       <c r="AJ21" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="AK21" t="s" s="2">
-        <v>66</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3464,16 +3367,16 @@
         <v>36</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>69</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>71</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>72</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3511,19 +3414,19 @@
         <v>36</v>
       </c>
       <c r="AB22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC22" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="AC22" t="s" s="2">
+      <c r="AD22" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE22" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="AD22" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AE22" t="s" s="2">
+      <c r="AF22" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>37</v>
@@ -3535,22 +3438,19 @@
         <v>36</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -3563,25 +3463,25 @@
         <v>36</v>
       </c>
       <c r="I23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="J23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K23" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="O23" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>36</v>
@@ -3630,7 +3530,7 @@
         <v>36</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>37</v>
@@ -3642,18 +3542,15 @@
         <v>36</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3679,10 +3576,10 @@
         <v>43</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3733,7 +3630,7 @@
         <v>36</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>37</v>
@@ -3745,18 +3642,15 @@
         <v>36</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK24" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3782,10 +3676,10 @@
         <v>43</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3836,7 +3730,7 @@
         <v>36</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>37</v>
@@ -3848,18 +3742,15 @@
         <v>36</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK25" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3885,10 +3776,10 @@
         <v>43</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3939,7 +3830,7 @@
         <v>36</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>37</v>
@@ -3951,18 +3842,15 @@
         <v>36</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK26" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3988,10 +3876,10 @@
         <v>43</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4042,7 +3930,7 @@
         <v>36</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>37</v>
@@ -4054,18 +3942,15 @@
         <v>36</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK27" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4091,10 +3976,10 @@
         <v>43</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4145,7 +4030,7 @@
         <v>36</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>37</v>
@@ -4157,18 +4042,15 @@
         <v>36</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK28" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4194,10 +4076,10 @@
         <v>43</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4248,7 +4130,7 @@
         <v>36</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>37</v>
@@ -4260,18 +4142,15 @@
         <v>36</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK29" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4297,10 +4176,10 @@
         <v>43</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4351,7 +4230,7 @@
         <v>36</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>37</v>
@@ -4363,18 +4242,15 @@
         <v>36</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK30" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4400,10 +4276,10 @@
         <v>59</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4454,7 +4330,7 @@
         <v>36</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>37</v>
@@ -4468,16 +4344,13 @@
       <c r="AJ31" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="AK31" t="s" s="2">
-        <v>36</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4571,20 +4444,17 @@
       <c r="AJ32" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="AK32" t="s" s="2">
-        <v>66</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4603,16 +4473,16 @@
         <v>36</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>69</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>71</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>72</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4650,19 +4520,19 @@
         <v>36</v>
       </c>
       <c r="AB33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC33" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="AC33" t="s" s="2">
+      <c r="AD33" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE33" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="AD33" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AE33" t="s" s="2">
+      <c r="AF33" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>37</v>
@@ -4674,22 +4544,19 @@
         <v>36</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -4702,25 +4569,25 @@
         <v>36</v>
       </c>
       <c r="I34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="J34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K34" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="O34" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>36</v>
@@ -4769,7 +4636,7 @@
         <v>36</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>37</v>
@@ -4781,18 +4648,15 @@
         <v>36</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4818,10 +4682,10 @@
         <v>43</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4872,7 +4736,7 @@
         <v>36</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>37</v>
@@ -4884,18 +4748,15 @@
         <v>36</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK35" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4921,10 +4782,10 @@
         <v>43</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4975,7 +4836,7 @@
         <v>36</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>37</v>
@@ -4987,18 +4848,15 @@
         <v>36</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK36" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5024,10 +4882,10 @@
         <v>43</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5078,7 +4936,7 @@
         <v>36</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>37</v>
@@ -5090,18 +4948,15 @@
         <v>36</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK37" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5127,10 +4982,10 @@
         <v>43</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5181,7 +5036,7 @@
         <v>36</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>42</v>
@@ -5195,16 +5050,13 @@
       <c r="AJ38" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="AK38" t="s" s="2">
-        <v>36</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5230,10 +5082,10 @@
         <v>43</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5284,7 +5136,7 @@
         <v>36</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>37</v>
@@ -5296,18 +5148,15 @@
         <v>36</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK39" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5333,10 +5182,10 @@
         <v>43</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5387,7 +5236,7 @@
         <v>36</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>37</v>
@@ -5399,18 +5248,15 @@
         <v>36</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK40" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5436,10 +5282,10 @@
         <v>43</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5490,7 +5336,7 @@
         <v>36</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>37</v>
@@ -5502,18 +5348,15 @@
         <v>36</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK41" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5539,10 +5382,10 @@
         <v>51</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5593,7 +5436,7 @@
         <v>36</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>37</v>
@@ -5605,18 +5448,15 @@
         <v>36</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK42" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5639,13 +5479,13 @@
         <v>36</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5696,7 +5536,7 @@
         <v>36</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>37</v>
@@ -5708,18 +5548,15 @@
         <v>36</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK43" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5742,13 +5579,13 @@
         <v>36</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5799,7 +5636,7 @@
         <v>36</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>37</v>
@@ -5811,18 +5648,15 @@
         <v>36</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK44" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5845,13 +5679,13 @@
         <v>36</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5902,7 +5736,7 @@
         <v>36</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>37</v>
@@ -5914,18 +5748,15 @@
         <v>36</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK45" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5948,13 +5779,13 @@
         <v>36</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6005,7 +5836,7 @@
         <v>36</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>37</v>
@@ -6017,18 +5848,15 @@
         <v>36</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK46" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6054,10 +5882,10 @@
         <v>59</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6108,7 +5936,7 @@
         <v>36</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>37</v>
@@ -6122,16 +5950,13 @@
       <c r="AJ47" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="AK47" t="s" s="2">
-        <v>36</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6157,10 +5982,10 @@
         <v>43</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6225,20 +6050,17 @@
       <c r="AJ48" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="AK48" t="s" s="2">
-        <v>66</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6257,16 +6079,16 @@
         <v>36</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>69</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>71</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>72</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6304,19 +6126,19 @@
         <v>36</v>
       </c>
       <c r="AB49" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC49" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="AC49" t="s" s="2">
+      <c r="AD49" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE49" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="AD49" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AE49" t="s" s="2">
+      <c r="AF49" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>37</v>
@@ -6328,22 +6150,19 @@
         <v>36</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -6356,25 +6175,25 @@
         <v>36</v>
       </c>
       <c r="I50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="J50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="O50" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>36</v>
@@ -6423,7 +6242,7 @@
         <v>36</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>37</v>
@@ -6435,18 +6254,15 @@
         <v>36</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6472,10 +6288,10 @@
         <v>43</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6526,7 +6342,7 @@
         <v>36</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>37</v>
@@ -6538,18 +6354,15 @@
         <v>36</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK51" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6575,10 +6388,10 @@
         <v>59</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6629,7 +6442,7 @@
         <v>36</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>37</v>
@@ -6643,16 +6456,13 @@
       <c r="AJ52" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="AK52" t="s" s="2">
-        <v>36</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6678,10 +6488,10 @@
         <v>43</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6746,20 +6556,17 @@
       <c r="AJ53" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="AK53" t="s" s="2">
-        <v>66</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -6778,16 +6585,16 @@
         <v>36</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>69</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>71</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>72</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -6825,19 +6632,19 @@
         <v>36</v>
       </c>
       <c r="AB54" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC54" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="AC54" t="s" s="2">
+      <c r="AD54" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE54" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="AD54" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AE54" t="s" s="2">
+      <c r="AF54" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>37</v>
@@ -6849,22 +6656,19 @@
         <v>36</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -6877,25 +6681,25 @@
         <v>36</v>
       </c>
       <c r="I55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="J55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="O55" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>36</v>
@@ -6944,7 +6748,7 @@
         <v>36</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>37</v>
@@ -6956,18 +6760,15 @@
         <v>36</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6993,10 +6794,10 @@
         <v>43</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7047,7 +6848,7 @@
         <v>36</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>37</v>
@@ -7059,18 +6860,15 @@
         <v>36</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK56" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7093,13 +6891,13 @@
         <v>36</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7150,7 +6948,7 @@
         <v>36</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>37</v>
@@ -7164,16 +6962,13 @@
       <c r="AJ57" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="AK57" t="s" s="2">
-        <v>36</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7199,10 +6994,10 @@
         <v>43</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7267,20 +7062,17 @@
       <c r="AJ58" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="AK58" t="s" s="2">
-        <v>66</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -7299,16 +7091,16 @@
         <v>36</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>69</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>71</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>72</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7346,19 +7138,19 @@
         <v>36</v>
       </c>
       <c r="AB59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC59" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="AC59" t="s" s="2">
+      <c r="AD59" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE59" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="AD59" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AE59" t="s" s="2">
+      <c r="AF59" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>37</v>
@@ -7370,18 +7162,15 @@
         <v>36</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7398,25 +7187,25 @@
         <v>36</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>36</v>
@@ -7429,43 +7218,43 @@
         <v>36</v>
       </c>
       <c r="T60" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y60" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="U60" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="X60" t="s" s="2">
+      <c r="Z60" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Y60" t="s" s="2">
+      <c r="AA60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>37</v>
@@ -7479,16 +7268,13 @@
       <c r="AJ60" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="AK60" t="s" s="2">
-        <v>190</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7508,19 +7294,19 @@
         <v>36</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -7534,43 +7320,43 @@
         <v>36</v>
       </c>
       <c r="T61" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>37</v>
@@ -7584,16 +7370,13 @@
       <c r="AJ61" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="AK61" t="s" s="2">
-        <v>190</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7613,22 +7396,22 @@
         <v>36</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
         <v>43</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="O62" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>36</v>
@@ -7641,7 +7424,7 @@
         <v>36</v>
       </c>
       <c r="T62" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="U62" t="s" s="2">
         <v>36</v>
@@ -7677,7 +7460,7 @@
         <v>36</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>37</v>
@@ -7691,16 +7474,13 @@
       <c r="AJ62" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="AK62" t="s" s="2">
-        <v>206</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7720,16 +7500,16 @@
         <v>36</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
         <v>43</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7744,7 +7524,7 @@
         <v>36</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>36</v>
@@ -7780,7 +7560,7 @@
         <v>36</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>37</v>
@@ -7794,20 +7574,17 @@
       <c r="AJ63" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="AK63" t="s" s="2">
-        <v>212</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -7823,16 +7600,16 @@
         <v>36</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>43</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7847,7 +7624,7 @@
         <v>36</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>36</v>
@@ -7883,7 +7660,7 @@
         <v>36</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>37</v>
@@ -7897,20 +7674,17 @@
       <c r="AJ64" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="AK64" t="s" s="2">
-        <v>217</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -7926,19 +7700,19 @@
         <v>36</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>43</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -7952,7 +7726,7 @@
         <v>36</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>36</v>
@@ -7988,7 +7762,7 @@
         <v>36</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>37</v>
@@ -8002,20 +7776,17 @@
       <c r="AJ65" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="AK65" t="s" s="2">
-        <v>223</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -8031,16 +7802,16 @@
         <v>36</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
         <v>43</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8091,7 +7862,7 @@
         <v>36</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>37</v>
@@ -8105,20 +7876,17 @@
       <c r="AJ66" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="AK66" t="s" s="2">
-        <v>228</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -8134,16 +7902,16 @@
         <v>36</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
         <v>43</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8158,7 +7926,7 @@
         <v>36</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>36</v>
@@ -8194,7 +7962,7 @@
         <v>36</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>37</v>
@@ -8208,16 +7976,13 @@
       <c r="AJ67" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="AK67" t="s" s="2">
-        <v>233</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8237,19 +8002,19 @@
         <v>36</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
         <v>43</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -8299,7 +8064,7 @@
         <v>36</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>37</v>
@@ -8313,16 +8078,13 @@
       <c r="AJ68" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="AK68" t="s" s="2">
-        <v>239</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8342,20 +8104,20 @@
         <v>36</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>36</v>
@@ -8368,7 +8130,7 @@
         <v>36</v>
       </c>
       <c r="T69" t="s" s="2">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="U69" t="s" s="2">
         <v>36</v>
@@ -8404,7 +8166,7 @@
         <v>36</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>37</v>
@@ -8418,16 +8180,13 @@
       <c r="AJ69" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="AK69" t="s" s="2">
-        <v>247</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8453,10 +8212,10 @@
         <v>43</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8507,7 +8266,7 @@
         <v>36</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>37</v>
@@ -8519,18 +8278,15 @@
         <v>36</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK70" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8556,10 +8312,10 @@
         <v>43</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8610,7 +8366,7 @@
         <v>36</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>37</v>
@@ -8622,18 +8378,15 @@
         <v>36</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK71" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8659,10 +8412,10 @@
         <v>43</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8713,7 +8466,7 @@
         <v>36</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>37</v>
@@ -8725,18 +8478,15 @@
         <v>36</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK72" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8762,10 +8512,10 @@
         <v>43</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8792,11 +8542,11 @@
         <v>36</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>36</v>
@@ -8814,7 +8564,7 @@
         <v>36</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>37</v>
@@ -8826,18 +8576,15 @@
         <v>36</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK73" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8863,10 +8610,10 @@
         <v>43</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -8893,11 +8640,11 @@
         <v>36</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>36</v>
@@ -8915,7 +8662,7 @@
         <v>36</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>37</v>
@@ -8927,18 +8674,15 @@
         <v>36</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK74" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8964,10 +8708,10 @@
         <v>43</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9018,7 +8762,7 @@
         <v>36</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>37</v>
@@ -9030,18 +8774,15 @@
         <v>36</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK75" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9067,10 +8808,10 @@
         <v>43</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9121,7 +8862,7 @@
         <v>36</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>37</v>
@@ -9133,18 +8874,15 @@
         <v>36</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK76" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9170,10 +8908,10 @@
         <v>43</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9200,11 +8938,11 @@
         <v>36</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>36</v>
@@ -9222,7 +8960,7 @@
         <v>36</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>37</v>
@@ -9234,18 +8972,15 @@
         <v>36</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK77" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9271,10 +9006,10 @@
         <v>43</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9301,11 +9036,11 @@
         <v>36</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>36</v>
@@ -9323,7 +9058,7 @@
         <v>36</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>37</v>
@@ -9335,18 +9070,15 @@
         <v>36</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK78" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9372,10 +9104,10 @@
         <v>43</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9402,11 +9134,11 @@
         <v>36</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>36</v>
@@ -9424,7 +9156,7 @@
         <v>36</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>37</v>
@@ -9436,18 +9168,15 @@
         <v>36</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK79" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9473,10 +9202,10 @@
         <v>51</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9527,7 +9256,7 @@
         <v>36</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>37</v>
@@ -9539,18 +9268,15 @@
         <v>36</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK80" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9576,10 +9302,10 @@
         <v>51</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9630,7 +9356,7 @@
         <v>36</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>37</v>
@@ -9642,18 +9368,15 @@
         <v>36</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK81" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9679,10 +9402,10 @@
         <v>43</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9709,11 +9432,11 @@
         <v>36</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>36</v>
@@ -9731,7 +9454,7 @@
         <v>36</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>37</v>
@@ -9743,18 +9466,15 @@
         <v>36</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK82" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9780,10 +9500,10 @@
         <v>59</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9834,7 +9554,7 @@
         <v>36</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>42</v>
@@ -9848,16 +9568,13 @@
       <c r="AJ83" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="AK83" t="s" s="2">
-        <v>36</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9883,10 +9600,10 @@
         <v>43</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -9951,20 +9668,17 @@
       <c r="AJ84" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="AK84" t="s" s="2">
-        <v>66</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -9983,16 +9697,16 @@
         <v>36</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>69</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>71</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>72</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -10030,19 +9744,19 @@
         <v>36</v>
       </c>
       <c r="AB85" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC85" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="AC85" t="s" s="2">
+      <c r="AD85" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE85" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="AD85" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AE85" t="s" s="2">
+      <c r="AF85" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>37</v>
@@ -10054,22 +9768,19 @@
         <v>36</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -10082,25 +9793,25 @@
         <v>36</v>
       </c>
       <c r="I86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="J86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="O86" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>36</v>
@@ -10149,7 +9860,7 @@
         <v>36</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>37</v>
@@ -10161,18 +9872,15 @@
         <v>36</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10198,10 +9906,10 @@
         <v>43</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10252,7 +9960,7 @@
         <v>36</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>37</v>
@@ -10264,18 +9972,15 @@
         <v>36</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK87" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10301,10 +10006,10 @@
         <v>51</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10355,7 +10060,7 @@
         <v>36</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>37</v>
@@ -10367,18 +10072,15 @@
         <v>36</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK88" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10404,10 +10106,10 @@
         <v>43</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10458,7 +10160,7 @@
         <v>36</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>42</v>
@@ -10470,18 +10172,15 @@
         <v>36</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK89" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10507,10 +10206,10 @@
         <v>43</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10561,7 +10260,7 @@
         <v>36</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>37</v>
@@ -10573,18 +10272,15 @@
         <v>36</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK90" t="s" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10610,10 +10306,10 @@
         <v>43</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -10664,7 +10360,7 @@
         <v>36</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>42</v>
@@ -10676,9 +10372,6 @@
         <v>36</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AK91" t="s" s="2">
         <v>36</v>
       </c>
     </row>

--- a/refs/heads/main/StructureDefinition-CertDIVOC.xlsx
+++ b/refs/heads/main/StructureDefinition-CertDIVOC.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-30T07:55:09+00:00</t>
+    <t>2024-07-30T11:13:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
